--- a/astro-site/public/dl/kit-gestion-personal/02-control-horas-extras.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/02-control-horas-extras.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Registro Horas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Resumen Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Horas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Registro Horas'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Resumen Mensual'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="€#,##0.00" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -129,41 +132,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="2" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -523,15 +526,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -539,6 +543,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -567,9 +572,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -605,9 +608,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -636,8 +637,25 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -646,19 +664,19 @@
   <sheetPr>
     <tabColor rgb="00E65100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="16"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="16"/>
-    <col customWidth="1" max="8" min="8" width="18"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -675,6 +693,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1517,6 +1536,7 @@
       </c>
       <c r="H54" s="9" t="n"/>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
@@ -1531,11 +1551,20 @@
     <mergeCell ref="A56:H56"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Voluntaria,Obligatoria"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1544,18 +1573,18 @@
   <sheetPr>
     <tabColor rgb="00BF360C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
-    <col customWidth="1" max="6" min="6" width="18"/>
-    <col customWidth="1" max="7" min="7" width="18"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1582,6 +1611,7 @@
         <v>12</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -1934,6 +1964,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
@@ -1942,21 +1973,22 @@
       </c>
       <c r="B22" s="16">
         <f>SUM(B6:B20)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="14">
         <f>SUM(E6:E20)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F22" s="14">
         <f>SUM(F6:F20)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="14">
         <f>SUM(G6:G20)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -1970,6 +2002,15 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/02-control-horas-extras.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/02-control-horas-extras.xlsx
@@ -1,20 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Horas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registro Horas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Registro Horas'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Resumen Mensual'!$5:$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
+    <numFmt formatCode="€#,##0.00" numFmtId="164"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -132,41 +129,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="2" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -526,16 +523,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="B2:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -543,7 +539,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -572,7 +567,9 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -608,7 +605,9 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="B14" t="inlineStr"/>
+    </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -637,25 +636,8 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -664,19 +646,19 @@
   <sheetPr>
     <tabColor rgb="00E65100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="16"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="16"/>
+    <col customWidth="1" max="8" min="8" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,7 +675,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1536,7 +1517,6 @@
       </c>
       <c r="H54" s="9" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
@@ -1551,20 +1531,11 @@
     <mergeCell ref="A56:H56"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54" type="list">
       <formula1>"Voluntaria,Obligatoria"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1573,18 +1544,18 @@
   <sheetPr>
     <tabColor rgb="00BF360C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="16"/>
+    <col customWidth="1" max="3" min="3" width="16"/>
+    <col customWidth="1" max="4" min="4" width="16"/>
+    <col customWidth="1" max="5" min="5" width="18"/>
+    <col customWidth="1" max="6" min="6" width="18"/>
+    <col customWidth="1" max="7" min="7" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1611,7 +1582,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -1964,7 +1934,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
@@ -1973,22 +1942,21 @@
       </c>
       <c r="B22" s="16">
         <f>SUM(B6:B20)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E22" s="14">
         <f>SUM(E6:E20)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="F22" s="14">
         <f>SUM(F6:F20)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="G22" s="14">
         <f>SUM(G6:G20)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23"/>
+        <v/>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -2002,15 +1970,6 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>